--- a/source_data/10_validation_guides/2025_7_new_validation_guides.xlsx
+++ b/source_data/10_validation_guides/2025_7_new_validation_guides.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/samgould/Documents/GitHub/CDK-BE-mutagenesis/source_data/10_validation_guides/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BA77934-928D-0346-98F5-75E24BAA2F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01C19059-5169-1447-936B-370881DC6175}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="81">
   <si>
     <t>CDK8_834_T</t>
   </si>
@@ -213,13 +214,76 @@
   </si>
   <si>
     <t>GTTATGAGACAGCTCATGGA</t>
+  </si>
+  <si>
+    <t>gRNA #</t>
+  </si>
+  <si>
+    <t>gRNA Name</t>
+  </si>
+  <si>
+    <t>Gene</t>
+  </si>
+  <si>
+    <t>Variant</t>
+  </si>
+  <si>
+    <t>CDK8</t>
+  </si>
+  <si>
+    <t>CDK9</t>
+  </si>
+  <si>
+    <t>CDK12</t>
+  </si>
+  <si>
+    <t>Editor</t>
+  </si>
+  <si>
+    <t>CDK13</t>
+  </si>
+  <si>
+    <t>CBE</t>
+  </si>
+  <si>
+    <t>ABE</t>
+  </si>
+  <si>
+    <t>I733V</t>
+  </si>
+  <si>
+    <t>G731K</t>
+  </si>
+  <si>
+    <t>G822K</t>
+  </si>
+  <si>
+    <t>M816I_D817N</t>
+  </si>
+  <si>
+    <t>G822E</t>
+  </si>
+  <si>
+    <t>I711V_T715A</t>
+  </si>
+  <si>
+    <t>M818V_R819G</t>
+  </si>
+  <si>
+    <t>I711V</t>
+  </si>
+  <si>
+    <t>C106Y_E107K</t>
+  </si>
+  <si>
+    <t>V159A</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -231,6 +295,43 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFCCCCCC"/>
+      <name val="Menlo"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="7"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="4"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -256,9 +357,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -989,5 +1096,215 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E501DE65-A043-644C-939D-7CD6AEB7DF39}">
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="2" max="2" width="17.1640625" customWidth="1"/>
+    <col min="5" max="5" width="14.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="E2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" s="3"/>
+    </row>
+    <row r="16" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="C16" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/source_data/10_validation_guides/2025_7_new_validation_guides.xlsx
+++ b/source_data/10_validation_guides/2025_7_new_validation_guides.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/samgould/Documents/GitHub/CDK-BE-mutagenesis/source_data/10_validation_guides/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01C19059-5169-1447-936B-370881DC6175}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53CAD290-73E6-614E-B0AD-E688DBE3A3D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/source_data/10_validation_guides/2025_7_new_validation_guides.xlsx
+++ b/source_data/10_validation_guides/2025_7_new_validation_guides.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/samgould/Documents/GitHub/CDK-BE-mutagenesis/source_data/10_validation_guides/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53CAD290-73E6-614E-B0AD-E688DBE3A3D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86015088-40E5-7944-B5D0-A90231D65A5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7400" yWindow="760" windowWidth="30240" windowHeight="17720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -357,7 +357,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -365,12 +365,32 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -918,7 +938,7 @@
         <v>46</v>
       </c>
       <c r="F10" t="str">
-        <f t="shared" si="0"/>
+        <f>RIGHT(B10, 20)</f>
         <v>GTATTGGAGAAGGTACTTAC</v>
       </c>
       <c r="G10" t="s">
@@ -1102,15 +1122,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E501DE65-A043-644C-939D-7CD6AEB7DF39}">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="17.1640625" customWidth="1"/>
     <col min="5" max="5" width="14.1640625" customWidth="1"/>
+    <col min="6" max="6" width="12.1640625" customWidth="1"/>
+    <col min="8" max="8" width="21" customWidth="1"/>
+    <col min="10" max="10" width="17.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>60</v>
       </c>
@@ -1126,8 +1149,9 @@
       <c r="E1" s="1" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1144,7 +1168,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1161,7 +1185,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1174,11 +1198,11 @@
       <c r="D4" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1191,11 +1215,11 @@
       <c r="D5" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1208,11 +1232,11 @@
       <c r="D6" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E6" s="7" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1225,11 +1249,11 @@
       <c r="D7" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E7" s="7" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1242,11 +1266,11 @@
       <c r="D8" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1259,11 +1283,11 @@
       <c r="D9" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1276,11 +1300,11 @@
       <c r="D10" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E10" s="7" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E10" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1293,17 +1317,27 @@
       <c r="D11" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E11" s="7" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E11" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="3"/>
     </row>
-    <row r="16" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="C16" s="4"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="I1:I24">
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="CDK12">
+      <formula>NOT(ISERROR(SEARCH("CDK12",I1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K1:K24">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="CBE">
+      <formula>NOT(ISERROR(SEARCH("CBE",K1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
